--- a/per-stock/DELL/financials.xlsx
+++ b/per-stock/DELL/financials.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (annual)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (quarterly)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance sheet (annual)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (annual)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data flags" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="FY Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Income stmt (annual)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Income stmt (quarterly)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Balance sheet (annual)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Balance sheet (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Cash flow (annual)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Cash flow (quarterly)" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Data flags" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +24,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -61,11 +67,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -531,7 +540,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>157339172864</v>
+        <v>264595308544</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -546,7 +555,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>176991666176</v>
+        <v>285743218688</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -561,7 +570,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.846952</v>
+        <v>32.681564</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -576,7 +585,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16.399164</v>
+        <v>19.180435</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -591,7 +600,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.3857843</v>
+        <v>1.9745624</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -606,7 +615,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.20125</v>
+        <v>0.19212</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -621,7 +630,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.09623</v>
+        <v>0.08857000600000001</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -636,7 +645,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.05228</v>
+        <v>0.062750004</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -668,7 +677,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.395</v>
+        <v>0.875</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -683,7 +692,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>11532999680</v>
+        <v>11580999680</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -698,7 +707,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>32259999744</v>
+        <v>31924000768</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -713,11 +722,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>6606750208</v>
+        <v>9442000000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>yfinance info.freeCashflow</t>
+          <t>statement: TTM OCF - |capex| (yfinance quarterly_cashflow)</t>
         </is>
       </c>
     </row>
@@ -728,7 +737,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>325654621</v>
+        <v>325046693</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -743,7 +752,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>241.99</v>
+        <v>409.5</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -787,6 +796,477 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Fiscal-year summary (GAAP, $ except where noted)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>FY-3</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>FY-2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>FY-1</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>TTM</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Source / formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Fiscal period end</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2024-01-31</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>TTM → 2026-04-30</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>annual statement headers; TTM = Σ last 4 quarters</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>'Income stmt (annual)'!D49</f>
+        <v/>
+      </c>
+      <c r="C3" s="3">
+        <f>'Income stmt (annual)'!C49</f>
+        <v/>
+      </c>
+      <c r="D3" s="3">
+        <f>'Income stmt (annual)'!B49</f>
+        <v/>
+      </c>
+      <c r="E3" s="3">
+        <f>SUM('Income stmt (quarterly)'!B45:E45)</f>
+        <v/>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>'Income stmt (annual)'!D47</f>
+        <v/>
+      </c>
+      <c r="C4" s="3">
+        <f>'Income stmt (annual)'!C47</f>
+        <v/>
+      </c>
+      <c r="D4" s="3">
+        <f>'Income stmt (annual)'!B47</f>
+        <v/>
+      </c>
+      <c r="E4" s="3">
+        <f>SUM('Income stmt (quarterly)'!B43:E43)</f>
+        <v/>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gross Profit (GAAP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B5" s="4">
+        <f>IFERROR(B4/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C5" s="4">
+        <f>IFERROR(C4/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D5" s="4">
+        <f>IFERROR(D4/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E5" s="4">
+        <f>IFERROR(E4/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>GAAP = gross profit / revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Operating income</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>'Income stmt (annual)'!D43</f>
+        <v/>
+      </c>
+      <c r="C6" s="3">
+        <f>'Income stmt (annual)'!C43</f>
+        <v/>
+      </c>
+      <c r="D6" s="3">
+        <f>'Income stmt (annual)'!B43</f>
+        <v/>
+      </c>
+      <c r="E6" s="3">
+        <f>SUM('Income stmt (quarterly)'!B39:E39)</f>
+        <v/>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Operating Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Operating margin %</t>
+        </is>
+      </c>
+      <c r="B7" s="4">
+        <f>IFERROR(B6/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C7" s="4">
+        <f>IFERROR(C6/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D7" s="4">
+        <f>IFERROR(D6/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E7" s="4">
+        <f>IFERROR(E6/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F7">
+        <f> operating income / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>'Income stmt (annual)'!D10</f>
+        <v/>
+      </c>
+      <c r="C8" s="3">
+        <f>'Income stmt (annual)'!C10</f>
+        <v/>
+      </c>
+      <c r="D8" s="3">
+        <f>'Income stmt (annual)'!B10</f>
+        <v/>
+      </c>
+      <c r="E8" s="3">
+        <f>SUM('Income stmt (quarterly)'!B10:E10)</f>
+        <v/>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Free cash flow</t>
+        </is>
+      </c>
+      <c r="B9" s="3">
+        <f>'Cash flow (annual)'!D2</f>
+        <v/>
+      </c>
+      <c r="C9" s="3">
+        <f>'Cash flow (annual)'!C2</f>
+        <v/>
+      </c>
+      <c r="D9" s="3">
+        <f>'Cash flow (annual)'!B2</f>
+        <v/>
+      </c>
+      <c r="E9" s="3">
+        <f>SUM('Cash flow (quarterly)'!B2:E2)</f>
+        <v/>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>FCF = OCF − capex</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FCF margin %</t>
+        </is>
+      </c>
+      <c r="B10" s="4">
+        <f>IFERROR(B9/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C10" s="4">
+        <f>IFERROR(C9/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D10" s="4">
+        <f>IFERROR(D9/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E10" s="4">
+        <f>IFERROR(E9/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F10">
+        <f> FCF / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Capex</t>
+        </is>
+      </c>
+      <c r="B11" s="3">
+        <f>-'Cash flow (annual)'!D7</f>
+        <v/>
+      </c>
+      <c r="C11" s="3">
+        <f>-'Cash flow (annual)'!C7</f>
+        <v/>
+      </c>
+      <c r="D11" s="3">
+        <f>-'Cash flow (annual)'!B7</f>
+        <v/>
+      </c>
+      <c r="E11" s="3">
+        <f>-SUM('Cash flow (quarterly)'!B7:E7)</f>
+        <v/>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Capex (shown positive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Capex / revenue %</t>
+        </is>
+      </c>
+      <c r="B12" s="4">
+        <f>IFERROR(B11/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C12" s="4">
+        <f>IFERROR(C11/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D12" s="4">
+        <f>IFERROR(D11/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E12" s="4">
+        <f>IFERROR(E11/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f> capex / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Net debt</t>
+        </is>
+      </c>
+      <c r="B13" s="3">
+        <f>'Balance sheet (annual)'!D5</f>
+        <v/>
+      </c>
+      <c r="C13" s="3">
+        <f>'Balance sheet (annual)'!C5</f>
+        <v/>
+      </c>
+      <c r="D13" s="3">
+        <f>'Balance sheet (annual)'!B5</f>
+        <v/>
+      </c>
+      <c r="E13" s="3">
+        <f>'Balance sheet (quarterly)'!B5</f>
+        <v/>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Net debt; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Net debt / EBITDA</t>
+        </is>
+      </c>
+      <c r="B14" s="5">
+        <f>IFERROR(B13/B8,"")</f>
+        <v/>
+      </c>
+      <c r="C14" s="5">
+        <f>IFERROR(C13/C8,"")</f>
+        <v/>
+      </c>
+      <c r="D14" s="5">
+        <f>IFERROR(D13/D8,"")</f>
+        <v/>
+      </c>
+      <c r="E14" s="5">
+        <f>IFERROR(E13/E8,"")</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f> net debt / EBITDA</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Share count (period-end, M)</t>
+        </is>
+      </c>
+      <c r="B15" s="6">
+        <f>'Balance sheet (annual)'!D3/1e6</f>
+        <v/>
+      </c>
+      <c r="C15" s="6">
+        <f>'Balance sheet (annual)'!C3/1e6</f>
+        <v/>
+      </c>
+      <c r="D15" s="6">
+        <f>'Balance sheet (annual)'!B3/1e6</f>
+        <v/>
+      </c>
+      <c r="E15" s="6">
+        <f>'Balance sheet (quarterly)'!B3/1e6</f>
+        <v/>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>shares ÷ 1e6; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Share count YoY %</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr"/>
+      <c r="C16" s="4">
+        <f>IFERROR(C15/B15-1,"")</f>
+        <v/>
+      </c>
+      <c r="D16" s="4">
+        <f>IFERROR(D15/C15-1,"")</f>
+        <v/>
+      </c>
+      <c r="E16" s="4">
+        <f>IFERROR(E15/D15-1,"")</f>
+        <v/>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>vs prior period</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1182,10 +1662,10 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>683870968</v>
+        <v>684000000</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>719749216</v>
+        <v>720000000</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>706335200</v>
@@ -1202,10 +1682,10 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>662689605</v>
+        <v>675000000</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>696130464</v>
+        <v>705000000</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>706335200</v>
@@ -1242,10 +1722,10 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>8.957436</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>6.596465</v>
+        <v>6.51</v>
       </c>
       <c r="D22" s="3" t="n">
         <v>4.546</v>
@@ -1810,13 +2290,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1826,6 +2306,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1836,30 +2317,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2026-01-31</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2025-10-31</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2025-07-31</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2025-04-30</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>2025-01-31</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>2024-10-31</t>
         </is>
@@ -1872,21 +2358,22 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>65623100.303951</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>-5980707.395498</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="D2" s="3" t="n">
         <v>17574000</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="E2" s="3" t="n">
         <v>-2108333.333333</v>
       </c>
-      <c r="E2" s="3" t="n">
-        <v>27021237.303786</v>
-      </c>
       <c r="F2" s="3" t="n">
-        <v>27315094.339623</v>
+        <v>19721144.967682</v>
       </c>
       <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1895,21 +2382,22 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>0.129179</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>0.192926</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="D3" s="3" t="n">
         <v>0.202</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="E3" s="3" t="n">
         <v>0.191667</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="F3" s="3" t="n">
         <v>0.108957</v>
       </c>
-      <c r="F3" s="3" t="n">
-        <v>0.220283</v>
-      </c>
       <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1918,21 +2406,22 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>4601000000</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>4014000000</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="D4" s="3" t="n">
         <v>3006000000</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="E4" s="3" t="n">
         <v>2612000000</v>
       </c>
-      <c r="E4" s="3" t="n">
-        <v>1934000000</v>
-      </c>
       <c r="F4" s="3" t="n">
-        <v>3114000000</v>
+        <v>2001000000</v>
       </c>
       <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1941,21 +2430,22 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
+        <v>508000000</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>-31000000</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="D5" s="3" t="n">
         <v>87000000</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="E5" s="3" t="n">
         <v>-11000000</v>
       </c>
-      <c r="E5" s="3" t="n">
-        <v>248000000</v>
-      </c>
       <c r="F5" s="3" t="n">
-        <v>124000000</v>
+        <v>181000000</v>
       </c>
       <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1964,21 +2454,22 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
+        <v>508000000</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>-31000000</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="D6" s="3" t="n">
         <v>87000000</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="E6" s="3" t="n">
         <v>-11000000</v>
       </c>
-      <c r="E6" s="3" t="n">
-        <v>248000000</v>
-      </c>
       <c r="F6" s="3" t="n">
-        <v>124000000</v>
+        <v>181000000</v>
       </c>
       <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1987,21 +2478,22 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>3438000000</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>2259000000</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="D7" s="3" t="n">
         <v>1548000000</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="E7" s="3" t="n">
         <v>1164000000</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="F7" s="3" t="n">
         <v>965000000</v>
       </c>
-      <c r="F7" s="3" t="n">
-        <v>1654000000</v>
-      </c>
       <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2010,21 +2502,22 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
+        <v>758000000</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>773000000</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="D8" s="3" t="n">
         <v>756000000</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="E8" s="3" t="n">
         <v>762000000</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="F8" s="3" t="n">
         <v>738000000</v>
       </c>
-      <c r="F8" s="3" t="n">
-        <v>774000000</v>
-      </c>
       <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2033,21 +2526,22 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
+        <v>36060000000</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>26649000000</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="D9" s="3" t="n">
         <v>21412000000</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="E9" s="3" t="n">
         <v>24329000000</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="F9" s="3" t="n">
         <v>18441000000</v>
       </c>
-      <c r="F9" s="3" t="n">
-        <v>18105000000</v>
-      </c>
       <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2056,21 +2550,22 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>5109000000</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>3983000000</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="D10" s="3" t="n">
         <v>3093000000</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="E10" s="3" t="n">
         <v>2601000000</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="F10" s="3" t="n">
         <v>2182000000</v>
       </c>
-      <c r="F10" s="3" t="n">
-        <v>3238000000</v>
-      </c>
       <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2079,21 +2574,22 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
+        <v>4351000000</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>3210000000</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="D11" s="3" t="n">
         <v>2337000000</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="E11" s="3" t="n">
         <v>1839000000</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="F11" s="3" t="n">
         <v>1444000000</v>
       </c>
-      <c r="F11" s="3" t="n">
-        <v>2464000000</v>
-      </c>
       <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2102,21 +2598,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
+        <v>-322000000</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>-315000000</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="D12" s="3" t="n">
         <v>-314000000</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="E12" s="3" t="n">
         <v>-322000000</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="F12" s="3" t="n">
         <v>-330000000</v>
       </c>
-      <c r="F12" s="3" t="n">
-        <v>-311000000</v>
-      </c>
       <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2125,21 +2622,22 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
+        <v>403000000</v>
+      </c>
+      <c r="C13" s="3" t="n">
         <v>411000000</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="D13" s="3" t="n">
         <v>396000000</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="E13" s="3" t="n">
         <v>399000000</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="F13" s="3" t="n">
         <v>361000000</v>
       </c>
-      <c r="F13" s="3" t="n">
-        <v>344000000</v>
-      </c>
       <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2148,21 +2646,22 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
+        <v>81000000</v>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>96000000</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="D14" s="3" t="n">
         <v>82000000</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="E14" s="3" t="n">
         <v>77000000</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="F14" s="3" t="n">
         <v>31000000</v>
       </c>
-      <c r="F14" s="3" t="n">
-        <v>33000000</v>
-      </c>
       <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2171,21 +2670,22 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
+        <v>2995623100.303951</v>
+      </c>
+      <c r="C15" s="3" t="n">
         <v>2284019292.604502</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="D15" s="3" t="n">
         <v>1478574000</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="E15" s="3" t="n">
         <v>1172891666.666667</v>
       </c>
-      <c r="E15" s="3" t="n">
-        <v>744021237.303786</v>
-      </c>
       <c r="F15" s="3" t="n">
-        <v>1557315094.339623</v>
+        <v>803721144.967682</v>
       </c>
       <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2194,21 +2694,22 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
+        <v>3438000000</v>
+      </c>
+      <c r="C16" s="3" t="n">
         <v>2259000000</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="D16" s="3" t="n">
         <v>1548000000</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="E16" s="3" t="n">
         <v>1164000000</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="F16" s="3" t="n">
         <v>965000000</v>
       </c>
-      <c r="F16" s="3" t="n">
-        <v>1654000000</v>
-      </c>
       <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2217,21 +2718,22 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
+        <v>40080000000</v>
+      </c>
+      <c r="C17" s="3" t="n">
         <v>30234000000</v>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="D17" s="3" t="n">
         <v>24837000000</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="E17" s="3" t="n">
         <v>28003000000</v>
       </c>
-      <c r="E17" s="3" t="n">
-        <v>22213000000</v>
-      </c>
       <c r="F17" s="3" t="n">
-        <v>21624000000</v>
+        <v>22146000000</v>
       </c>
       <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2240,21 +2742,22 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
+        <v>3656000000</v>
+      </c>
+      <c r="C18" s="3" t="n">
         <v>3092000000</v>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="D18" s="3" t="n">
         <v>2119000000</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="E18" s="3" t="n">
         <v>1773000000</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="F18" s="3" t="n">
         <v>1165000000</v>
       </c>
-      <c r="F18" s="3" t="n">
-        <v>2307000000</v>
-      </c>
       <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2263,21 +2766,22 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
+        <v>656000000</v>
+      </c>
+      <c r="C19" s="3" t="n">
         <v>670326409</v>
       </c>
-      <c r="C19" s="3" t="n">
-        <v>678947368</v>
-      </c>
       <c r="D19" s="3" t="n">
-        <v>684705882</v>
+        <v>680000000</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>704379562</v>
+        <v>686000000</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>713023256</v>
+        <v>702000000</v>
       </c>
       <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2286,21 +2790,22 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
+        <v>649000000</v>
+      </c>
+      <c r="C20" s="3" t="n">
         <v>651771798</v>
       </c>
-      <c r="C20" s="3" t="n">
-        <v>666762341</v>
-      </c>
       <c r="D20" s="3" t="n">
-        <v>674708671</v>
+        <v>671000000</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>683477567</v>
+        <v>678000000</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>696130464</v>
+        <v>692000000</v>
       </c>
       <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2309,21 +2814,22 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="C21" s="3" t="n">
         <v>3.37</v>
       </c>
-      <c r="C21" s="3" t="n">
+      <c r="D21" s="3" t="n">
         <v>2.28</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="E21" s="3" t="n">
         <v>1.7</v>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="F21" s="3" t="n">
         <v>1.37</v>
       </c>
-      <c r="F21" s="3" t="n">
-        <v>2.15</v>
-      </c>
       <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2332,21 +2838,22 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="C22" s="3" t="n">
         <v>3.465937</v>
       </c>
-      <c r="C22" s="3" t="n">
-        <v>2.321667</v>
-      </c>
       <c r="D22" s="3" t="n">
-        <v>1.720922</v>
+        <v>2.31</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>1.411897</v>
+        <v>1.72</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>2.202173</v>
+        <v>1.39</v>
       </c>
       <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2355,21 +2862,22 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
+        <v>3438000000</v>
+      </c>
+      <c r="C23" s="3" t="n">
         <v>2259000000</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="D23" s="3" t="n">
         <v>1548000000</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="E23" s="3" t="n">
         <v>1164000000</v>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="F23" s="3" t="n">
         <v>965000000</v>
       </c>
-      <c r="F23" s="3" t="n">
-        <v>1654000000</v>
-      </c>
       <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2378,21 +2886,22 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
+        <v>3438000000</v>
+      </c>
+      <c r="C24" s="3" t="n">
         <v>2259000000</v>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="D24" s="3" t="n">
         <v>1548000000</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="E24" s="3" t="n">
         <v>1164000000</v>
       </c>
-      <c r="E24" s="3" t="n">
+      <c r="F24" s="3" t="n">
         <v>965000000</v>
       </c>
-      <c r="F24" s="3" t="n">
-        <v>1654000000</v>
-      </c>
       <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2401,21 +2910,22 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
+        <v>3438000000</v>
+      </c>
+      <c r="C25" s="3" t="n">
         <v>2259000000</v>
       </c>
-      <c r="C25" s="3" t="n">
+      <c r="D25" s="3" t="n">
         <v>1548000000</v>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="E25" s="3" t="n">
         <v>1164000000</v>
       </c>
-      <c r="E25" s="3" t="n">
+      <c r="F25" s="3" t="n">
         <v>965000000</v>
       </c>
-      <c r="F25" s="3" t="n">
-        <v>1654000000</v>
-      </c>
       <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2423,9 +2933,7 @@
           <t>Minority Interests</t>
         </is>
       </c>
-      <c r="B26" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="B26" s="3" t="n"/>
       <c r="C26" s="3" t="n">
         <v>0</v>
       </c>
@@ -2436,9 +2944,12 @@
         <v>0</v>
       </c>
       <c r="F26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="3" t="n">
         <v>1000000</v>
       </c>
-      <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2447,21 +2958,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
+        <v>3438000000</v>
+      </c>
+      <c r="C27" s="3" t="n">
         <v>2259000000</v>
       </c>
-      <c r="C27" s="3" t="n">
+      <c r="D27" s="3" t="n">
         <v>1548000000</v>
       </c>
-      <c r="D27" s="3" t="n">
+      <c r="E27" s="3" t="n">
         <v>1164000000</v>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="F27" s="3" t="n">
         <v>965000000</v>
       </c>
-      <c r="F27" s="3" t="n">
-        <v>1653000000</v>
-      </c>
       <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2470,21 +2982,22 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
+        <v>3438000000</v>
+      </c>
+      <c r="C28" s="3" t="n">
         <v>2259000000</v>
       </c>
-      <c r="C28" s="3" t="n">
+      <c r="D28" s="3" t="n">
         <v>1548000000</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="E28" s="3" t="n">
         <v>1164000000</v>
       </c>
-      <c r="E28" s="3" t="n">
+      <c r="F28" s="3" t="n">
         <v>965000000</v>
       </c>
-      <c r="F28" s="3" t="n">
-        <v>1653000000</v>
-      </c>
       <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2493,21 +3006,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
+        <v>510000000</v>
+      </c>
+      <c r="C29" s="3" t="n">
         <v>540000000</v>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="D29" s="3" t="n">
         <v>393000000</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="E29" s="3" t="n">
         <v>276000000</v>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="F29" s="3" t="n">
         <v>118000000</v>
       </c>
-      <c r="F29" s="3" t="n">
-        <v>467000000</v>
-      </c>
       <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2516,21 +3030,22 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
+        <v>3948000000</v>
+      </c>
+      <c r="C30" s="3" t="n">
         <v>2799000000</v>
       </c>
-      <c r="C30" s="3" t="n">
+      <c r="D30" s="3" t="n">
         <v>1941000000</v>
       </c>
-      <c r="D30" s="3" t="n">
+      <c r="E30" s="3" t="n">
         <v>1440000000</v>
       </c>
-      <c r="E30" s="3" t="n">
+      <c r="F30" s="3" t="n">
         <v>1083000000</v>
       </c>
-      <c r="F30" s="3" t="n">
-        <v>2120000000</v>
-      </c>
       <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2539,21 +3054,22 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
+        <v>508000000</v>
+      </c>
+      <c r="C31" s="3" t="n">
         <v>-31000000</v>
       </c>
-      <c r="C31" s="3" t="n">
+      <c r="D31" s="3" t="n">
         <v>87000000</v>
       </c>
-      <c r="D31" s="3" t="n">
+      <c r="E31" s="3" t="n">
         <v>-11000000</v>
       </c>
-      <c r="E31" s="3" t="n">
-        <v>248000000</v>
-      </c>
       <c r="F31" s="3" t="n">
-        <v>124000000</v>
+        <v>181000000</v>
       </c>
       <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2562,21 +3078,22 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
+        <v>-106000000</v>
+      </c>
+      <c r="C32" s="3" t="n">
         <v>-53000000</v>
       </c>
-      <c r="C32" s="3" t="n">
+      <c r="D32" s="3" t="n">
         <v>-49000000</v>
       </c>
-      <c r="D32" s="3" t="n">
+      <c r="E32" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E32" s="3" t="n">
-        <v>236000000</v>
-      </c>
-      <c r="F32" s="3" t="n"/>
-      <c r="G32" s="3" t="n">
-        <v>-71000000</v>
-      </c>
+      <c r="F32" s="3" t="n">
+        <v>169000000</v>
+      </c>
+      <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2594,12 +3111,13 @@
         <v>0</v>
       </c>
       <c r="E33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="3" t="n">
         <v>236000000</v>
       </c>
-      <c r="F33" s="3" t="n"/>
-      <c r="G33" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2608,15 +3126,20 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
+        <v>106000000</v>
+      </c>
+      <c r="C34" s="3" t="n">
         <v>53000000</v>
       </c>
-      <c r="C34" s="3" t="n">
+      <c r="D34" s="3" t="n">
         <v>49000000</v>
       </c>
-      <c r="D34" s="3" t="n"/>
       <c r="E34" s="3" t="n"/>
-      <c r="F34" s="3" t="n"/>
-      <c r="G34" s="3" t="n">
+      <c r="F34" s="3" t="n">
+        <v>67000000</v>
+      </c>
+      <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n">
         <v>71000000</v>
       </c>
     </row>
@@ -2627,21 +3150,22 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
+        <v>614000000</v>
+      </c>
+      <c r="C35" s="3" t="n">
         <v>22000000</v>
       </c>
-      <c r="C35" s="3" t="n">
+      <c r="D35" s="3" t="n">
         <v>136000000</v>
       </c>
-      <c r="D35" s="3" t="n">
+      <c r="E35" s="3" t="n">
         <v>-11000000</v>
       </c>
-      <c r="E35" s="3" t="n">
+      <c r="F35" s="3" t="n">
         <v>12000000</v>
       </c>
-      <c r="F35" s="3" t="n">
-        <v>124000000</v>
-      </c>
       <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2650,21 +3174,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
+        <v>-322000000</v>
+      </c>
+      <c r="C36" s="3" t="n">
         <v>-315000000</v>
       </c>
-      <c r="C36" s="3" t="n">
+      <c r="D36" s="3" t="n">
         <v>-314000000</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="E36" s="3" t="n">
         <v>-322000000</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="F36" s="3" t="n">
         <v>-330000000</v>
       </c>
-      <c r="F36" s="3" t="n">
-        <v>-311000000</v>
-      </c>
       <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2673,21 +3198,22 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
+        <v>403000000</v>
+      </c>
+      <c r="C37" s="3" t="n">
         <v>411000000</v>
       </c>
-      <c r="C37" s="3" t="n">
+      <c r="D37" s="3" t="n">
         <v>396000000</v>
       </c>
-      <c r="D37" s="3" t="n">
+      <c r="E37" s="3" t="n">
         <v>399000000</v>
       </c>
-      <c r="E37" s="3" t="n">
+      <c r="F37" s="3" t="n">
         <v>361000000</v>
       </c>
-      <c r="F37" s="3" t="n">
-        <v>344000000</v>
-      </c>
       <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2696,21 +3222,22 @@
         </is>
       </c>
       <c r="B38" s="3" t="n">
+        <v>81000000</v>
+      </c>
+      <c r="C38" s="3" t="n">
         <v>96000000</v>
       </c>
-      <c r="C38" s="3" t="n">
+      <c r="D38" s="3" t="n">
         <v>82000000</v>
       </c>
-      <c r="D38" s="3" t="n">
+      <c r="E38" s="3" t="n">
         <v>77000000</v>
       </c>
-      <c r="E38" s="3" t="n">
+      <c r="F38" s="3" t="n">
         <v>31000000</v>
       </c>
-      <c r="F38" s="3" t="n">
-        <v>33000000</v>
-      </c>
       <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2719,21 +3246,22 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
+        <v>3762000000</v>
+      </c>
+      <c r="C39" s="3" t="n">
         <v>3145000000</v>
       </c>
-      <c r="C39" s="3" t="n">
+      <c r="D39" s="3" t="n">
         <v>2168000000</v>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="E39" s="3" t="n">
         <v>1773000000</v>
       </c>
-      <c r="E39" s="3" t="n">
-        <v>1165000000</v>
-      </c>
       <c r="F39" s="3" t="n">
-        <v>2307000000</v>
+        <v>1232000000</v>
       </c>
       <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2742,21 +3270,22 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
+        <v>4020000000</v>
+      </c>
+      <c r="C40" s="3" t="n">
         <v>3585000000</v>
       </c>
-      <c r="C40" s="3" t="n">
+      <c r="D40" s="3" t="n">
         <v>3425000000</v>
       </c>
-      <c r="D40" s="3" t="n">
+      <c r="E40" s="3" t="n">
         <v>3674000000</v>
       </c>
-      <c r="E40" s="3" t="n">
-        <v>3772000000</v>
-      </c>
       <c r="F40" s="3" t="n">
-        <v>3519000000</v>
+        <v>3705000000</v>
       </c>
       <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2765,21 +3294,22 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
+        <v>983000000</v>
+      </c>
+      <c r="C41" s="3" t="n">
         <v>797000000</v>
       </c>
-      <c r="C41" s="3" t="n">
+      <c r="D41" s="3" t="n">
         <v>752000000</v>
       </c>
-      <c r="D41" s="3" t="n">
+      <c r="E41" s="3" t="n">
         <v>785000000</v>
       </c>
-      <c r="E41" s="3" t="n">
+      <c r="F41" s="3" t="n">
         <v>808000000</v>
       </c>
-      <c r="F41" s="3" t="n">
-        <v>773000000</v>
-      </c>
       <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2788,21 +3318,22 @@
         </is>
       </c>
       <c r="B42" s="3" t="n">
+        <v>3037000000</v>
+      </c>
+      <c r="C42" s="3" t="n">
         <v>2788000000</v>
       </c>
-      <c r="C42" s="3" t="n">
+      <c r="D42" s="3" t="n">
         <v>2673000000</v>
       </c>
-      <c r="D42" s="3" t="n">
+      <c r="E42" s="3" t="n">
         <v>2889000000</v>
       </c>
-      <c r="E42" s="3" t="n">
-        <v>2964000000</v>
-      </c>
       <c r="F42" s="3" t="n">
-        <v>2746000000</v>
+        <v>2897000000</v>
       </c>
       <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2811,21 +3342,22 @@
         </is>
       </c>
       <c r="B43" s="3" t="n">
+        <v>7782000000</v>
+      </c>
+      <c r="C43" s="3" t="n">
         <v>6730000000</v>
       </c>
-      <c r="C43" s="3" t="n">
+      <c r="D43" s="3" t="n">
         <v>5593000000</v>
       </c>
-      <c r="D43" s="3" t="n">
+      <c r="E43" s="3" t="n">
         <v>5447000000</v>
       </c>
-      <c r="E43" s="3" t="n">
+      <c r="F43" s="3" t="n">
         <v>4937000000</v>
       </c>
-      <c r="F43" s="3" t="n">
-        <v>5826000000</v>
-      </c>
       <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2834,21 +3366,22 @@
         </is>
       </c>
       <c r="B44" s="3" t="n">
+        <v>36060000000</v>
+      </c>
+      <c r="C44" s="3" t="n">
         <v>26649000000</v>
       </c>
-      <c r="C44" s="3" t="n">
+      <c r="D44" s="3" t="n">
         <v>21412000000</v>
       </c>
-      <c r="D44" s="3" t="n">
+      <c r="E44" s="3" t="n">
         <v>24329000000</v>
       </c>
-      <c r="E44" s="3" t="n">
+      <c r="F44" s="3" t="n">
         <v>18441000000</v>
       </c>
-      <c r="F44" s="3" t="n">
-        <v>18105000000</v>
-      </c>
       <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2857,21 +3390,22 @@
         </is>
       </c>
       <c r="B45" s="3" t="n">
+        <v>43842000000</v>
+      </c>
+      <c r="C45" s="3" t="n">
         <v>33379000000</v>
       </c>
-      <c r="C45" s="3" t="n">
+      <c r="D45" s="3" t="n">
         <v>27005000000</v>
       </c>
-      <c r="D45" s="3" t="n">
+      <c r="E45" s="3" t="n">
         <v>29776000000</v>
       </c>
-      <c r="E45" s="3" t="n">
+      <c r="F45" s="3" t="n">
         <v>23378000000</v>
       </c>
-      <c r="F45" s="3" t="n">
-        <v>23931000000</v>
-      </c>
       <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2880,28 +3414,29 @@
         </is>
       </c>
       <c r="B46" s="3" t="n">
+        <v>43842000000</v>
+      </c>
+      <c r="C46" s="3" t="n">
         <v>33379000000</v>
       </c>
-      <c r="C46" s="3" t="n">
+      <c r="D46" s="3" t="n">
         <v>27005000000</v>
       </c>
-      <c r="D46" s="3" t="n">
+      <c r="E46" s="3" t="n">
         <v>29776000000</v>
       </c>
-      <c r="E46" s="3" t="n">
+      <c r="F46" s="3" t="n">
         <v>23378000000</v>
       </c>
-      <c r="F46" s="3" t="n">
-        <v>23931000000</v>
-      </c>
       <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4353,7 +4888,1627 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H66"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2025-04-30</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>2024-10-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Treasury Shares Number</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>203000000</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>192000000</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>177000000</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>168000000</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>160000000</v>
+      </c>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Ordinary Shares Number</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>648534099</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>651771798</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>666762341</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>674708671</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>683477567</v>
+      </c>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Share Issued</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>851534099</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>843771798</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>843762341</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>842708671</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>843477567</v>
+      </c>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Net Debt</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>19583000000</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>19975000000</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>21674000000</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>20544000000</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>21081000000</v>
+      </c>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Total Debt</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>31161000000</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>31503000000</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>31243000000</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>28689000000</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>28781000000</v>
+      </c>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Tangible Book Value</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>-25347000000</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>-26550000000</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>-26606000000</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>-26850000000</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>-27207000000</v>
+      </c>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Invested Capital</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>29757000000</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>29033000000</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>28623000000</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>25923000000</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>25757000000</v>
+      </c>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Working Capital</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>-3991000000</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>-5667000000</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>-7414000000</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>-9350000000</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>-7497000000</v>
+      </c>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Net Tangible Assets</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>-25347000000</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>-26550000000</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>-26606000000</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>-26850000000</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>-27207000000</v>
+      </c>
+      <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Common Stock Equity</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>-1404000000</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>-2470000000</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>-2620000000</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>-2766000000</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>-3024000000</v>
+      </c>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Total Capitalization</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>22207000000</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>21043000000</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>21229000000</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>18769000000</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>20912000000</v>
+      </c>
+      <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Total Equity Gross Minority Interest</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>-1404000000</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>-2470000000</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>-2620000000</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>-2766000000</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>-3024000000</v>
+      </c>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Minority Interest</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n"/>
+      <c r="C14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>95000000</v>
+      </c>
+      <c r="H14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Stockholders Equity</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>-1404000000</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>-2470000000</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>-2620000000</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>-2766000000</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>-3024000000</v>
+      </c>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Gains Losses Not Affecting Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>-709000000</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>-719000000</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>-654000000</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>-710000000</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>-926000000</v>
+      </c>
+      <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Other Equity Adjustments</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>-709000000</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>-719000000</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>-654000000</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>-710000000</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>-926000000</v>
+      </c>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Treasury Stock</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>16149000000</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>14533000000</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>12665000000</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>11419000000</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>10488000000</v>
+      </c>
+      <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>6343000000</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>3325000000</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>1420000000</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>231000000</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>-567000000</v>
+      </c>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Capital Stock</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>9111000000</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>9457000000</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>9279000000</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>9132000000</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>8957000000</v>
+      </c>
+      <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Common Stock</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>9111000000</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>9457000000</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>9279000000</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>9132000000</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>8957000000</v>
+      </c>
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Total Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>116317000000</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>103756000000</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>90099000000</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>91942000000</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>89893000000</v>
+      </c>
+      <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Total Non Current Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>41719000000</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>40487000000</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>39583000000</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>37080000000</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>39471000000</v>
+      </c>
+      <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Other Non Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>3849000000</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>3378000000</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>3275000000</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>3123000000</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>3122000000</v>
+      </c>
+      <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>14259000000</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>13596000000</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>12459000000</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>12422000000</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>12413000000</v>
+      </c>
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Revenue</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>14259000000</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>13596000000</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>12459000000</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>12422000000</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>12413000000</v>
+      </c>
+      <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Long Term Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>23611000000</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>23513000000</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>23849000000</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>21535000000</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>23936000000</v>
+      </c>
+      <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Long Term Debt</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>23611000000</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>23513000000</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>23849000000</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>21535000000</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>23936000000</v>
+      </c>
+      <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>74598000000</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>63269000000</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>50516000000</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>54862000000</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>50422000000</v>
+      </c>
+      <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Other Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n"/>
+      <c r="C30" s="3" t="n"/>
+      <c r="D30" s="3" t="n"/>
+      <c r="E30" s="3" t="n"/>
+      <c r="F30" s="3" t="n"/>
+      <c r="G30" s="3" t="n">
+        <v>221000000</v>
+      </c>
+      <c r="H30" s="3" t="n">
+        <v>211000000</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>13193000000</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>13334000000</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>12649000000</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>13759000000</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>13907000000</v>
+      </c>
+      <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Current Deferred Revenue</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>13193000000</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>13334000000</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>12649000000</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>13759000000</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>13907000000</v>
+      </c>
+      <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Current Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>7550000000</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>7990000000</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>7394000000</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>7154000000</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>4845000000</v>
+      </c>
+      <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Current Debt</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>7550000000</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>7990000000</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>7394000000</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>7154000000</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>4845000000</v>
+      </c>
+      <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Payables And Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>53855000000</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>41945000000</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>30473000000</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>33949000000</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>31670000000</v>
+      </c>
+      <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Current Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>8594000000</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>8315000000</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>6679000000</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>6486000000</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>6321000000</v>
+      </c>
+      <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Payables</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>45261000000</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>33630000000</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>23794000000</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>27463000000</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>25349000000</v>
+      </c>
+      <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Accounts Payable</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>45261000000</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>33630000000</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>23794000000</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>27463000000</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>25349000000</v>
+      </c>
+      <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total Assets</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>114913000000</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>101286000000</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>87479000000</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>89176000000</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>86869000000</v>
+      </c>
+      <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Total Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>44306000000</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>43684000000</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>44377000000</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>43664000000</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>43944000000</v>
+      </c>
+      <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Other Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>5221000000</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>5376000000</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>5368000000</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>5455000000</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>5745000000</v>
+      </c>
+      <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Non Current Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>5713000000</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>5822000000</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>6725000000</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>6071000000</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>6042000000</v>
+      </c>
+      <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Investments And Advances</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>2484000000</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>1730000000</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>1760000000</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>1596000000</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>1591000000</v>
+      </c>
+      <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Goodwill And Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>23943000000</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>24080000000</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>23986000000</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>24084000000</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>24183000000</v>
+      </c>
+      <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>4439000000</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>4533000000</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>4628000000</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>4748000000</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>4868000000</v>
+      </c>
+      <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Goodwill</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>19504000000</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>19547000000</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>19358000000</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>19336000000</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>19315000000</v>
+      </c>
+      <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Net PPE</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>6945000000</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>6676000000</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>6538000000</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>6458000000</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>6383000000</v>
+      </c>
+      <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Accumulated Depreciation</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>-8500000000</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>-8167000000</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>-8718000000</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>-8559000000</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>-8265000000</v>
+      </c>
+      <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Gross PPE</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>15445000000</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>14843000000</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>15256000000</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>15017000000</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>14648000000</v>
+      </c>
+      <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Other Properties</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>6217000000</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>5777000000</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>5634000000</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>5673000000</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>5559000000</v>
+      </c>
+      <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Machinery Furniture Equipment</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>6077000000</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>5932000000</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>6570000000</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>6381000000</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>6195000000</v>
+      </c>
+      <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Properties</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>3151000000</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>3134000000</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>3052000000</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>2963000000</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>2894000000</v>
+      </c>
+      <c r="G52" s="3" t="n"/>
+      <c r="H52" s="3" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Current Assets</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v>70607000000</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>57602000000</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>43102000000</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>45512000000</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>42925000000</v>
+      </c>
+      <c r="G53" s="3" t="n"/>
+      <c r="H53" s="3" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Other Current Assets</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>9886000000</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>9594000000</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>8436000000</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>9181000000</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>12644000000</v>
+      </c>
+      <c r="G54" s="3" t="n"/>
+      <c r="H54" s="3" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Assets Held For Sale Current</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n"/>
+      <c r="C55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" s="3" t="n">
+        <v>668000000</v>
+      </c>
+      <c r="H55" s="3" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v>15052000000</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>10437000000</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>6949000000</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>7211000000</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>7415000000</v>
+      </c>
+      <c r="G56" s="3" t="n"/>
+      <c r="H56" s="3" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Finished Goods</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v>935000000</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>969000000</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>1085000000</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>931000000</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>941000000</v>
+      </c>
+      <c r="G57" s="3" t="n"/>
+      <c r="H57" s="3" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Work In Process</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>3483000000</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>2772000000</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>1268000000</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>1603000000</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>1229000000</v>
+      </c>
+      <c r="G58" s="3" t="n"/>
+      <c r="H58" s="3" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Raw Materials</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v>10634000000</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>6696000000</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>4596000000</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>4677000000</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>5245000000</v>
+      </c>
+      <c r="G59" s="3" t="n"/>
+      <c r="H59" s="3" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Receivables</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v>34091000000</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>26043000000</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>18148000000</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>20975000000</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>15166000000</v>
+      </c>
+      <c r="G60" s="3" t="n"/>
+      <c r="H60" s="3" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Other Receivables</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v>8237000000</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>8458000000</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>6427000000</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>5952000000</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>5381000000</v>
+      </c>
+      <c r="G61" s="3" t="n"/>
+      <c r="H61" s="3" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>25854000000</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>17585000000</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>11721000000</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>15023000000</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>9785000000</v>
+      </c>
+      <c r="G62" s="3" t="n"/>
+      <c r="H62" s="3" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Allowance For Doubtful Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v>-77000000</v>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>-77000000</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>-75000000</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>-83000000</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>-82000000</v>
+      </c>
+      <c r="G63" s="3" t="n"/>
+      <c r="H63" s="3" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Gross Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v>25931000000</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>17662000000</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>11796000000</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>15106000000</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>9867000000</v>
+      </c>
+      <c r="G64" s="3" t="n"/>
+      <c r="H64" s="3" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Cash Cash Equivalents And Short Term Investments</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="n">
+        <v>11578000000</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>11528000000</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>9569000000</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>8145000000</v>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>7700000000</v>
+      </c>
+      <c r="G65" s="3" t="n"/>
+      <c r="H65" s="3" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Cash And Cash Equivalents</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v>11578000000</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>11528000000</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>9569000000</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>8145000000</v>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>7700000000</v>
+      </c>
+      <c r="G66" s="3" t="n"/>
+      <c r="H66" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5370,13 +7525,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:H50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5386,6 +7541,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5396,30 +7552,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2026-01-31</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2025-10-31</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2025-07-31</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2025-04-30</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>2025-01-31</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>2024-10-31</t>
         </is>
@@ -5432,21 +7593,22 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>3118000000</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>3953000000</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="D2" s="3" t="n">
         <v>503000000</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="E2" s="3" t="n">
         <v>1868000000</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="F2" s="3" t="n">
         <v>2228000000</v>
       </c>
-      <c r="F2" s="3" t="n">
-        <v>-150000000</v>
-      </c>
       <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5455,21 +7617,22 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>-2165000000</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>-1858000000</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="D3" s="3" t="n">
         <v>-1269000000</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="E3" s="3" t="n">
         <v>-945000000</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="F3" s="3" t="n">
         <v>-2332000000</v>
       </c>
-      <c r="F3" s="3" t="n">
-        <v>-751000000</v>
-      </c>
       <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5478,21 +7641,22 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>-2788000000</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>-1121000000</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="D4" s="3" t="n">
         <v>-3977000000</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="E4" s="3" t="n">
         <v>-1114000000</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="F4" s="3" t="n">
         <v>-2310000000</v>
       </c>
-      <c r="F4" s="3" t="n">
-        <v>-976000000</v>
-      </c>
       <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5501,21 +7665,22 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
+        <v>2465000000</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>1232000000</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="D5" s="3" t="n">
         <v>6502000000</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="E5" s="3" t="n">
         <v>962000000</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="F5" s="3" t="n">
         <v>6308000000</v>
       </c>
-      <c r="F5" s="3" t="n">
-        <v>645000000</v>
-      </c>
       <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5523,20 +7688,21 @@
           <t>Issuance Of Capital Stock</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n">
+      <c r="B6" s="3" t="n"/>
+      <c r="C6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="D6" s="3" t="n">
         <v>4000000</v>
       </c>
-      <c r="D6" s="3" t="n"/>
       <c r="E6" s="3" t="n"/>
-      <c r="F6" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="F6" s="3" t="n"/>
       <c r="G6" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="H6" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5545,21 +7711,22 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>-963000000</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>-721000000</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="D7" s="3" t="n">
         <v>-669000000</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="E7" s="3" t="n">
         <v>-675000000</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="F7" s="3" t="n">
         <v>-568000000</v>
       </c>
-      <c r="F7" s="3" t="n">
-        <v>-735000000</v>
-      </c>
       <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5568,21 +7735,22 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
+        <v>11753000000</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>11706000000</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="D8" s="3" t="n">
         <v>9733000000</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="E8" s="3" t="n">
         <v>8291000000</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="F8" s="3" t="n">
         <v>7853000000</v>
       </c>
-      <c r="F8" s="3" t="n">
-        <v>3819000000</v>
-      </c>
       <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5591,21 +7759,22 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
+        <v>11706000000</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>9733000000</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="D9" s="3" t="n">
         <v>8291000000</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="E9" s="3" t="n">
         <v>7853000000</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="F9" s="3" t="n">
         <v>3819000000</v>
       </c>
-      <c r="F9" s="3" t="n">
-        <v>5404000000</v>
-      </c>
       <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5614,21 +7783,22 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>-13000000</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>87000000</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="D10" s="3" t="n">
         <v>30000000</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="E10" s="3" t="n">
         <v>15000000</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="F10" s="3" t="n">
         <v>89000000</v>
       </c>
-      <c r="F10" s="3" t="n">
-        <v>-101000000</v>
-      </c>
       <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5637,21 +7807,22 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
+        <v>60000000</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>1886000000</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="D11" s="3" t="n">
         <v>1412000000</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="E11" s="3" t="n">
         <v>423000000</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="F11" s="3" t="n">
         <v>3945000000</v>
       </c>
-      <c r="F11" s="3" t="n">
-        <v>-1484000000</v>
-      </c>
       <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -5660,21 +7831,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
+        <v>-2954000000</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>-2093000000</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="D12" s="3" t="n">
         <v>857000000</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="E12" s="3" t="n">
         <v>-1465000000</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="F12" s="3" t="n">
         <v>1237000000</v>
       </c>
-      <c r="F12" s="3" t="n">
-        <v>-1391000000</v>
-      </c>
       <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5683,21 +7855,22 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
+        <v>-2954000000</v>
+      </c>
+      <c r="C13" s="3" t="n">
         <v>-2093000000</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="D13" s="3" t="n">
         <v>857000000</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="E13" s="3" t="n">
         <v>-1465000000</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="F13" s="3" t="n">
         <v>1237000000</v>
       </c>
-      <c r="F13" s="3" t="n">
-        <v>-1391000000</v>
-      </c>
       <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -5706,21 +7879,22 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
+        <v>-2000000</v>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="D14" s="3" t="n">
         <v>-52000000</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="E14" s="3" t="n">
         <v>-3000000</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="F14" s="3" t="n">
         <v>-33000000</v>
       </c>
-      <c r="F14" s="3" t="n">
-        <v>2000000</v>
-      </c>
       <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -5729,21 +7903,22 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
+        <v>-464000000</v>
+      </c>
+      <c r="C15" s="3" t="n">
         <v>-346000000</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="D15" s="3" t="n">
         <v>-351000000</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="E15" s="3" t="n">
         <v>-366000000</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="F15" s="3" t="n">
         <v>-396000000</v>
       </c>
-      <c r="F15" s="3" t="n">
-        <v>-311000000</v>
-      </c>
       <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -5752,21 +7927,22 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
+        <v>-464000000</v>
+      </c>
+      <c r="C16" s="3" t="n">
         <v>-346000000</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="D16" s="3" t="n">
         <v>-351000000</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="E16" s="3" t="n">
         <v>-366000000</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="F16" s="3" t="n">
         <v>-396000000</v>
       </c>
-      <c r="F16" s="3" t="n">
-        <v>-311000000</v>
-      </c>
       <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -5775,21 +7951,22 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
+        <v>-2165000000</v>
+      </c>
+      <c r="C17" s="3" t="n">
         <v>-1858000000</v>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="D17" s="3" t="n">
         <v>-1265000000</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="E17" s="3" t="n">
         <v>-944000000</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="F17" s="3" t="n">
         <v>-2332000000</v>
       </c>
-      <c r="F17" s="3" t="n">
-        <v>-751000000</v>
-      </c>
       <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -5798,21 +7975,22 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
+        <v>-2165000000</v>
+      </c>
+      <c r="C18" s="3" t="n">
         <v>-1858000000</v>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="D18" s="3" t="n">
         <v>-1269000000</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="E18" s="3" t="n">
         <v>-945000000</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="F18" s="3" t="n">
         <v>-2332000000</v>
       </c>
-      <c r="F18" s="3" t="n">
-        <v>-751000000</v>
-      </c>
       <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -5820,20 +7998,21 @@
           <t>Common Stock Issuance</t>
         </is>
       </c>
-      <c r="B19" s="3" t="n">
+      <c r="B19" s="3" t="n"/>
+      <c r="C19" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="D19" s="3" t="n">
         <v>4000000</v>
       </c>
-      <c r="D19" s="3" t="n"/>
       <c r="E19" s="3" t="n"/>
-      <c r="F19" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="F19" s="3" t="n"/>
       <c r="G19" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="H19" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -5842,21 +8021,22 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
+        <v>-323000000</v>
+      </c>
+      <c r="C20" s="3" t="n">
         <v>111000000</v>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="D20" s="3" t="n">
         <v>2525000000</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="E20" s="3" t="n">
         <v>-152000000</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="F20" s="3" t="n">
         <v>3998000000</v>
       </c>
-      <c r="F20" s="3" t="n">
-        <v>-331000000</v>
-      </c>
       <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -5865,21 +8045,22 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
+        <v>-323000000</v>
+      </c>
+      <c r="C21" s="3" t="n">
         <v>111000000</v>
       </c>
-      <c r="C21" s="3" t="n">
+      <c r="D21" s="3" t="n">
         <v>2525000000</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="E21" s="3" t="n">
         <v>-152000000</v>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="F21" s="3" t="n">
         <v>3998000000</v>
       </c>
-      <c r="F21" s="3" t="n">
-        <v>-331000000</v>
-      </c>
       <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -5888,21 +8069,22 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
+        <v>-2788000000</v>
+      </c>
+      <c r="C22" s="3" t="n">
         <v>-1121000000</v>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="D22" s="3" t="n">
         <v>-3977000000</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="E22" s="3" t="n">
         <v>-1114000000</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="F22" s="3" t="n">
         <v>-2310000000</v>
       </c>
-      <c r="F22" s="3" t="n">
-        <v>-976000000</v>
-      </c>
       <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -5911,21 +8093,22 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
+        <v>2465000000</v>
+      </c>
+      <c r="C23" s="3" t="n">
         <v>1232000000</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="D23" s="3" t="n">
         <v>6502000000</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="E23" s="3" t="n">
         <v>962000000</v>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="F23" s="3" t="n">
         <v>6308000000</v>
       </c>
-      <c r="F23" s="3" t="n">
-        <v>645000000</v>
-      </c>
       <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -5934,21 +8117,22 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
+        <v>-1067000000</v>
+      </c>
+      <c r="C24" s="3" t="n">
         <v>-695000000</v>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="D24" s="3" t="n">
         <v>-617000000</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="E24" s="3" t="n">
         <v>-655000000</v>
       </c>
-      <c r="E24" s="3" t="n">
+      <c r="F24" s="3" t="n">
         <v>-88000000</v>
       </c>
-      <c r="F24" s="3" t="n">
-        <v>-678000000</v>
-      </c>
       <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -5957,21 +8141,22 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
+        <v>-1067000000</v>
+      </c>
+      <c r="C25" s="3" t="n">
         <v>-695000000</v>
       </c>
-      <c r="C25" s="3" t="n">
+      <c r="D25" s="3" t="n">
         <v>-617000000</v>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="E25" s="3" t="n">
         <v>-655000000</v>
       </c>
-      <c r="E25" s="3" t="n">
+      <c r="F25" s="3" t="n">
         <v>-88000000</v>
       </c>
-      <c r="F25" s="3" t="n">
-        <v>-678000000</v>
-      </c>
       <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -5980,21 +8165,22 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
+        <v>19000000</v>
+      </c>
+      <c r="C26" s="3" t="n">
         <v>20000000</v>
       </c>
-      <c r="C26" s="3" t="n">
+      <c r="D26" s="3" t="n">
         <v>27000000</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="E26" s="3" t="n">
         <v>20000000</v>
       </c>
-      <c r="E26" s="3" t="n">
+      <c r="F26" s="3" t="n">
         <v>13000000</v>
       </c>
-      <c r="F26" s="3" t="n">
-        <v>54000000</v>
-      </c>
       <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -6003,21 +8189,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
+        <v>-123000000</v>
+      </c>
+      <c r="C27" s="3" t="n">
         <v>90000000</v>
       </c>
-      <c r="C27" s="3" t="n">
+      <c r="D27" s="3" t="n">
         <v>25000000</v>
       </c>
-      <c r="D27" s="3" t="n">
+      <c r="E27" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="F27" s="3" t="n">
         <v>-66000000</v>
       </c>
-      <c r="F27" s="3" t="n">
-        <v>3000000</v>
-      </c>
       <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -6026,21 +8213,22 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="C28" s="3" t="n">
         <v>116000000</v>
       </c>
-      <c r="C28" s="3" t="n">
+      <c r="D28" s="3" t="n">
         <v>71000000</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="E28" s="3" t="n">
         <v>28000000</v>
       </c>
-      <c r="E28" s="3" t="n">
+      <c r="F28" s="3" t="n">
         <v>31000000</v>
       </c>
-      <c r="F28" s="3" t="n">
-        <v>45000000</v>
-      </c>
       <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -6049,21 +8237,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
+        <v>-124000000</v>
+      </c>
+      <c r="C29" s="3" t="n">
         <v>-26000000</v>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="D29" s="3" t="n">
         <v>-46000000</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="E29" s="3" t="n">
         <v>-28000000</v>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="F29" s="3" t="n">
         <v>-97000000</v>
       </c>
-      <c r="F29" s="3" t="n">
-        <v>-42000000</v>
-      </c>
       <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -6072,21 +8261,22 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="3" t="n">
         <v>-84000000</v>
-      </c>
-      <c r="C30" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="3" t="n">
         <v>533000000</v>
       </c>
-      <c r="F30" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -6104,12 +8294,13 @@
         <v>0</v>
       </c>
       <c r="E31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="3" t="n">
         <v>533000000</v>
       </c>
-      <c r="F31" s="3" t="n"/>
-      <c r="G31" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -6121,10 +8312,11 @@
       <c r="C32" s="3" t="n"/>
       <c r="D32" s="3" t="n"/>
       <c r="E32" s="3" t="n"/>
-      <c r="F32" s="3" t="n">
+      <c r="F32" s="3" t="n"/>
+      <c r="G32" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -6133,21 +8325,22 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
+        <v>-963000000</v>
+      </c>
+      <c r="C33" s="3" t="n">
         <v>-721000000</v>
       </c>
-      <c r="C33" s="3" t="n">
+      <c r="D33" s="3" t="n">
         <v>-669000000</v>
       </c>
-      <c r="D33" s="3" t="n">
+      <c r="E33" s="3" t="n">
         <v>-675000000</v>
       </c>
-      <c r="E33" s="3" t="n">
+      <c r="F33" s="3" t="n">
         <v>-568000000</v>
       </c>
-      <c r="F33" s="3" t="n">
-        <v>-735000000</v>
-      </c>
       <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -6156,21 +8349,22 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
+        <v>4081000000</v>
+      </c>
+      <c r="C34" s="3" t="n">
         <v>4674000000</v>
       </c>
-      <c r="C34" s="3" t="n">
+      <c r="D34" s="3" t="n">
         <v>1172000000</v>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="E34" s="3" t="n">
         <v>2543000000</v>
       </c>
-      <c r="E34" s="3" t="n">
+      <c r="F34" s="3" t="n">
         <v>2796000000</v>
       </c>
-      <c r="F34" s="3" t="n">
-        <v>585000000</v>
-      </c>
       <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -6179,21 +8373,22 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
+        <v>4081000000</v>
+      </c>
+      <c r="C35" s="3" t="n">
         <v>4674000000</v>
       </c>
-      <c r="C35" s="3" t="n">
+      <c r="D35" s="3" t="n">
         <v>1172000000</v>
       </c>
-      <c r="D35" s="3" t="n">
+      <c r="E35" s="3" t="n">
         <v>2543000000</v>
       </c>
-      <c r="E35" s="3" t="n">
+      <c r="F35" s="3" t="n">
         <v>2796000000</v>
       </c>
-      <c r="F35" s="3" t="n">
-        <v>585000000</v>
-      </c>
       <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -6202,21 +8397,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
+        <v>38000000</v>
+      </c>
+      <c r="C36" s="3" t="n">
         <v>1221000000</v>
       </c>
-      <c r="C36" s="3" t="n">
+      <c r="D36" s="3" t="n">
         <v>-1457000000</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="E36" s="3" t="n">
         <v>94000000</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="F36" s="3" t="n">
         <v>985000000</v>
       </c>
-      <c r="F36" s="3" t="n">
-        <v>-2074000000</v>
-      </c>
       <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -6225,21 +8421,22 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
+        <v>1160000000</v>
+      </c>
+      <c r="C37" s="3" t="n">
         <v>1847000000</v>
       </c>
-      <c r="C37" s="3" t="n">
+      <c r="D37" s="3" t="n">
         <v>-142000000</v>
       </c>
-      <c r="D37" s="3" t="n">
+      <c r="E37" s="3" t="n">
         <v>3728000000</v>
       </c>
-      <c r="E37" s="3" t="n">
+      <c r="F37" s="3" t="n">
         <v>-3506000000</v>
       </c>
-      <c r="F37" s="3" t="n">
-        <v>301000000</v>
-      </c>
       <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -6248,21 +8445,22 @@
         </is>
       </c>
       <c r="B38" s="3" t="n">
+        <v>11661000000</v>
+      </c>
+      <c r="C38" s="3" t="n">
         <v>9746000000</v>
       </c>
-      <c r="C38" s="3" t="n">
+      <c r="D38" s="3" t="n">
         <v>-3696000000</v>
       </c>
-      <c r="D38" s="3" t="n">
+      <c r="E38" s="3" t="n">
         <v>2104000000</v>
       </c>
-      <c r="E38" s="3" t="n">
+      <c r="F38" s="3" t="n">
         <v>4511000000</v>
       </c>
-      <c r="F38" s="3" t="n">
-        <v>-2386000000</v>
-      </c>
       <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -6271,21 +8469,22 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
+        <v>11661000000</v>
+      </c>
+      <c r="C39" s="3" t="n">
         <v>9746000000</v>
       </c>
-      <c r="C39" s="3" t="n">
+      <c r="D39" s="3" t="n">
         <v>-3696000000</v>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="E39" s="3" t="n">
         <v>2104000000</v>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="F39" s="3" t="n">
         <v>4511000000</v>
       </c>
-      <c r="F39" s="3" t="n">
-        <v>-2386000000</v>
-      </c>
       <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -6294,21 +8493,22 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
+        <v>11661000000</v>
+      </c>
+      <c r="C40" s="3" t="n">
         <v>9746000000</v>
       </c>
-      <c r="C40" s="3" t="n">
+      <c r="D40" s="3" t="n">
         <v>-3696000000</v>
       </c>
-      <c r="D40" s="3" t="n">
+      <c r="E40" s="3" t="n">
         <v>2104000000</v>
       </c>
-      <c r="E40" s="3" t="n">
+      <c r="F40" s="3" t="n">
         <v>4511000000</v>
       </c>
-      <c r="F40" s="3" t="n">
-        <v>-2386000000</v>
-      </c>
       <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -6317,21 +8517,22 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
+        <v>-4715000000</v>
+      </c>
+      <c r="C41" s="3" t="n">
         <v>-3578000000</v>
       </c>
-      <c r="C41" s="3" t="n">
+      <c r="D41" s="3" t="n">
         <v>206000000</v>
       </c>
-      <c r="D41" s="3" t="n">
+      <c r="E41" s="3" t="n">
         <v>119000000</v>
       </c>
-      <c r="E41" s="3" t="n">
+      <c r="F41" s="3" t="n">
         <v>-734000000</v>
       </c>
-      <c r="F41" s="3" t="n">
-        <v>-193000000</v>
-      </c>
       <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -6340,21 +8541,22 @@
         </is>
       </c>
       <c r="B42" s="3" t="n">
+        <v>-8068000000</v>
+      </c>
+      <c r="C42" s="3" t="n">
         <v>-6794000000</v>
       </c>
-      <c r="C42" s="3" t="n">
+      <c r="D42" s="3" t="n">
         <v>2175000000</v>
       </c>
-      <c r="D42" s="3" t="n">
+      <c r="E42" s="3" t="n">
         <v>-5857000000</v>
       </c>
-      <c r="E42" s="3" t="n">
+      <c r="F42" s="3" t="n">
         <v>714000000</v>
       </c>
-      <c r="F42" s="3" t="n">
-        <v>204000000</v>
-      </c>
       <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -6363,21 +8565,22 @@
         </is>
       </c>
       <c r="B43" s="3" t="n">
+        <v>-8331000000</v>
+      </c>
+      <c r="C43" s="3" t="n">
         <v>-5758000000</v>
       </c>
-      <c r="C43" s="3" t="n">
+      <c r="D43" s="3" t="n">
         <v>3310000000</v>
       </c>
-      <c r="D43" s="3" t="n">
+      <c r="E43" s="3" t="n">
         <v>-5265000000</v>
       </c>
-      <c r="E43" s="3" t="n">
+      <c r="F43" s="3" t="n">
         <v>691000000</v>
       </c>
-      <c r="F43" s="3" t="n">
-        <v>736000000</v>
-      </c>
       <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -6386,21 +8589,22 @@
         </is>
       </c>
       <c r="B44" s="3" t="n">
+        <v>-387000000</v>
+      </c>
+      <c r="C44" s="3" t="n">
         <v>277000000</v>
       </c>
-      <c r="C44" s="3" t="n">
+      <c r="D44" s="3" t="n">
         <v>48000000</v>
       </c>
-      <c r="D44" s="3" t="n">
+      <c r="E44" s="3" t="n">
         <v>215000000</v>
       </c>
-      <c r="E44" s="3" t="n">
+      <c r="F44" s="3" t="n">
         <v>174000000</v>
       </c>
-      <c r="F44" s="3" t="n">
-        <v>-168000000</v>
-      </c>
       <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -6412,18 +8616,19 @@
         <v>189000000</v>
       </c>
       <c r="C45" s="3" t="n">
+        <v>189000000</v>
+      </c>
+      <c r="D45" s="3" t="n">
         <v>165000000</v>
       </c>
-      <c r="D45" s="3" t="n">
+      <c r="E45" s="3" t="n">
         <v>179000000</v>
       </c>
-      <c r="E45" s="3" t="n">
+      <c r="F45" s="3" t="n">
         <v>190000000</v>
       </c>
-      <c r="F45" s="3" t="n">
-        <v>186000000</v>
-      </c>
       <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -6432,21 +8637,22 @@
         </is>
       </c>
       <c r="B46" s="3" t="n">
+        <v>45000000</v>
+      </c>
+      <c r="C46" s="3" t="n">
         <v>-45000000</v>
       </c>
-      <c r="C46" s="3" t="n">
+      <c r="D46" s="3" t="n">
         <v>112000000</v>
       </c>
-      <c r="D46" s="3" t="n">
+      <c r="E46" s="3" t="n">
         <v>129000000</v>
       </c>
-      <c r="E46" s="3" t="n">
+      <c r="F46" s="3" t="n">
         <v>-256000000</v>
       </c>
-      <c r="F46" s="3" t="n">
-        <v>214000000</v>
-      </c>
       <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -6455,21 +8661,22 @@
         </is>
       </c>
       <c r="B47" s="3" t="n">
+        <v>45000000</v>
+      </c>
+      <c r="C47" s="3" t="n">
         <v>-45000000</v>
       </c>
-      <c r="C47" s="3" t="n">
+      <c r="D47" s="3" t="n">
         <v>112000000</v>
       </c>
-      <c r="D47" s="3" t="n">
+      <c r="E47" s="3" t="n">
         <v>129000000</v>
       </c>
-      <c r="E47" s="3" t="n">
+      <c r="F47" s="3" t="n">
         <v>-256000000</v>
       </c>
-      <c r="F47" s="3" t="n">
-        <v>214000000</v>
-      </c>
       <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -6478,21 +8685,22 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
+        <v>758000000</v>
+      </c>
+      <c r="C48" s="3" t="n">
         <v>773000000</v>
       </c>
-      <c r="C48" s="3" t="n">
+      <c r="D48" s="3" t="n">
         <v>756000000</v>
       </c>
-      <c r="D48" s="3" t="n">
+      <c r="E48" s="3" t="n">
         <v>762000000</v>
       </c>
-      <c r="E48" s="3" t="n">
+      <c r="F48" s="3" t="n">
         <v>738000000</v>
       </c>
-      <c r="F48" s="3" t="n">
-        <v>774000000</v>
-      </c>
       <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -6501,21 +8709,22 @@
         </is>
       </c>
       <c r="B49" s="3" t="n">
+        <v>758000000</v>
+      </c>
+      <c r="C49" s="3" t="n">
         <v>773000000</v>
       </c>
-      <c r="C49" s="3" t="n">
+      <c r="D49" s="3" t="n">
         <v>756000000</v>
       </c>
-      <c r="D49" s="3" t="n">
+      <c r="E49" s="3" t="n">
         <v>762000000</v>
       </c>
-      <c r="E49" s="3" t="n">
+      <c r="F49" s="3" t="n">
         <v>738000000</v>
       </c>
-      <c r="F49" s="3" t="n">
-        <v>774000000</v>
-      </c>
       <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -6524,28 +8733,29 @@
         </is>
       </c>
       <c r="B50" s="3" t="n">
+        <v>3438000000</v>
+      </c>
+      <c r="C50" s="3" t="n">
         <v>2259000000</v>
       </c>
-      <c r="C50" s="3" t="n">
+      <c r="D50" s="3" t="n">
         <v>1548000000</v>
       </c>
-      <c r="D50" s="3" t="n">
+      <c r="E50" s="3" t="n">
         <v>1164000000</v>
       </c>
-      <c r="E50" s="3" t="n">
+      <c r="F50" s="3" t="n">
         <v>965000000</v>
       </c>
-      <c r="F50" s="3" t="n">
-        <v>1653000000</v>
-      </c>
       <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
